--- a/liaisons_Super_Constellation/Reseau_American_Overseas_L1049_sourced.xlsx
+++ b/liaisons_Super_Constellation/Reseau_American_Overseas_L1049_sourced.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Atlantique Nord (illustratif)" sheetId="1" r:id="rId1"/>
+    <sheet name="Lignes DC-4" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,7 +433,7 @@
         <v>AO 101</v>
       </c>
       <c r="B2" t="str">
-        <v>Atlantique Nord (Flagship)</v>
+        <v>Atlantique Nord (Londres)</v>
       </c>
       <c r="C2" t="str">
         <v>New York (IDL)</v>
@@ -442,16 +442,16 @@
         <v>18:00</v>
       </c>
       <c r="E2" t="str">
-        <v>Gander [Tech] (20:30 / 21:30)</v>
+        <v>Gander [Tech] (23:00 / 00:15 *)</v>
       </c>
       <c r="F2" t="str">
-        <v>Shannon (05:00 * / 06:00 *)</v>
+        <v>Shannon (05:15 * / 06:15 *)</v>
       </c>
       <c r="G2" t="str">
         <v>Londres (LHR)</v>
       </c>
       <c r="H2" t="str">
-        <v>08:00 *</v>
+        <v>08:15 *</v>
       </c>
       <c r="I2" t="str">
         <v>Mardi, Jeudi, Samedi</v>
@@ -474,13 +474,13 @@
         <v>Shannon (14:00 / 15:00)</v>
       </c>
       <c r="F3" t="str">
-        <v>Gander [Tech] (22:30 / 23:30)</v>
+        <v>Gander [Tech] (20:00 / 21:15)</v>
       </c>
       <c r="G3" t="str">
         <v>New York (IDL)</v>
       </c>
       <c r="H3" t="str">
-        <v>02:00 *</v>
+        <v>02:15 *</v>
       </c>
       <c r="I3" t="str">
         <v>Mercredi, Vendredi, Dimanche</v>
@@ -491,7 +491,7 @@
         <v>AO 151</v>
       </c>
       <c r="B4" t="str">
-        <v>Route de Scandinavie</v>
+        <v>Scandinavie (Copenhague)</v>
       </c>
       <c r="C4" t="str">
         <v>New York (IDL)</v>
@@ -500,16 +500,16 @@
         <v>17:00</v>
       </c>
       <c r="E4" t="str">
-        <v>Gander [Tech] (19:30 / 20:30)</v>
+        <v>Gander [Tech] (22:00 / 23:15)</v>
       </c>
       <c r="F4" t="str">
-        <v>Prestwick (03:30 * / 04:30 *)</v>
+        <v>Prestwick (04:15 * / 05:15 *)</v>
       </c>
       <c r="G4" t="str">
         <v>Copenhague</v>
       </c>
       <c r="H4" t="str">
-        <v>07:00 *</v>
+        <v>07:45 *</v>
       </c>
       <c r="I4" t="str">
         <v>Lundi, Vendredi</v>
@@ -520,7 +520,7 @@
         <v>AO 152</v>
       </c>
       <c r="B5" t="str">
-        <v>Route de Scandinavie (Retour)</v>
+        <v>Scandinavie (Copenhague) (Retour)</v>
       </c>
       <c r="C5" t="str">
         <v>Copenhague</v>
@@ -532,13 +532,13 @@
         <v>Prestwick (12:30 / 13:30)</v>
       </c>
       <c r="F5" t="str">
-        <v>Gander [Tech] (20:30 / 21:30)</v>
+        <v>Gander [Tech] (18:30 / 19:45)</v>
       </c>
       <c r="G5" t="str">
         <v>New York (IDL)</v>
       </c>
       <c r="H5" t="str">
-        <v>00:00 *</v>
+        <v>00:45 *</v>
       </c>
       <c r="I5" t="str">
         <v>Mercredi, Dimanche</v>
@@ -604,7 +604,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ATTENTION : American Overseas Airlines a fusionné avec Pan Am en septembre 1950, AVANT l'entrée en service du L-1049 (déc. 1951) ; elle exploitait des Constellation L-049/L-749. Feuillet illustratif, ENTIÈREMENT RECONSTITUÉ [R].</v>
+        <v>Sources : American Overseas Airlines a exploité le Douglas DC-4 sur l'Atlantique Nord (New York–Europe/Scandinavie) de 1945 à sa fusion dans Pan Am en 1950.</v>
       </c>
       <c r="B8" t="str">
         <v/>
@@ -633,7 +633,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>[S] Sourcé : uniquement les corridors nord-atlantiques réels d'AOA — pas l'appareil L-1049.</v>
+        <v>Ligne exploitée historiquement en Douglas DC-4 ; proposée ici pour le Super Constellation L-1049, appareil de même catégorie (quadrimoteur à pistons long-courrier).</v>
       </c>
       <c r="B9" t="str">
         <v/>
@@ -662,7 +662,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>* Arrivée un jour plus tard (chaque * = +1 jour). [Tech] = escale technique. HL : Heure locale.</v>
+        <v>[R] Reconstitué : numéros de vol et horaires — non issus d'un timetable original.</v>
       </c>
       <c r="B10" t="str">
         <v/>
@@ -691,36 +691,65 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v>* Arrivée un jour plus tard (chaque * = +1 jour). [Tech] = escale technique. HL : Heure locale.</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
         <v>[R] Vols retour reconstitués par itinéraire miroir (horaires plausibles).</v>
       </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I12"/>
   </ignoredErrors>
 </worksheet>
 </file>